--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5C9567-B340-4FEB-9CBC-390B885A666D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5743E86C-CB4C-4CBA-A970-D00D0F266162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,12 @@
   </si>
   <si>
     <t>was busy in preparations mostly for my cousin's surprise birthday party</t>
+  </si>
+  <si>
+    <t>Attended my 1yrs old cousin's birthday party</t>
+  </si>
+  <si>
+    <t>Got my BCA's degree certificates from my college</t>
   </si>
 </sst>
 </file>
@@ -1807,54 +1813,102 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
         <v>46269</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="B22" s="14">
+        <v>500</v>
+      </c>
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>60</v>
+      </c>
+      <c r="E22" s="14">
+        <v>30</v>
+      </c>
+      <c r="F22" s="14">
+        <v>200</v>
+      </c>
+      <c r="G22" s="14">
+        <v>4</v>
+      </c>
+      <c r="H22" s="14">
+        <v>300</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+        <v>350</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B23" s="14">
+        <v>480</v>
+      </c>
+      <c r="C23" s="14">
+        <v>0</v>
+      </c>
+      <c r="D23" s="14">
+        <v>0</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>480</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
+      <c r="A24" s="13">
+        <v>46271</v>
+      </c>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5743E86C-CB4C-4CBA-A970-D00D0F266162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{266F2066-8B1F-4171-8DB4-E6A14F642E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -275,6 +275,15 @@
   </si>
   <si>
     <t>Got my BCA's degree certificates from my college</t>
+  </si>
+  <si>
+    <t>Went to chandigarh to visit a well known temple there</t>
+  </si>
+  <si>
+    <t>My two wheeler broke down on my way to home from college and I got home at 9 pm</t>
+  </si>
+  <si>
+    <t>Regular Tuesday : performed voluntary service at temple</t>
   </si>
 </sst>
 </file>
@@ -1905,73 +1914,143 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
         <v>46271</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="B24" s="14">
+        <v>450</v>
+      </c>
+      <c r="C24" s="14">
+        <v>30</v>
+      </c>
+      <c r="D24" s="14">
+        <v>120</v>
+      </c>
+      <c r="E24" s="14">
+        <v>30</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>420</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+        <v>390</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B25" s="14">
+        <v>360</v>
+      </c>
+      <c r="C25" s="14">
+        <v>30</v>
+      </c>
+      <c r="D25" s="14">
+        <v>100</v>
+      </c>
+      <c r="E25" s="14">
+        <v>0</v>
+      </c>
+      <c r="F25" s="14">
+        <v>200</v>
+      </c>
+      <c r="G25" s="14">
+        <v>4</v>
+      </c>
+      <c r="H25" s="14">
+        <v>520</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+        <v>230</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B26" s="14">
+        <v>400</v>
+      </c>
+      <c r="C26" s="14">
+        <v>0</v>
+      </c>
+      <c r="D26" s="14">
+        <v>0</v>
+      </c>
+      <c r="E26" s="14">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14">
+        <v>300</v>
+      </c>
+      <c r="G26" s="14">
+        <v>6</v>
+      </c>
+      <c r="H26" s="14">
+        <v>240</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{266F2066-8B1F-4171-8DB4-E6A14F642E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB75F44F-1C27-4EDB-ADB7-956E39346965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,12 @@
   </si>
   <si>
     <t>Regular Tuesday : performed voluntary service at temple</t>
+  </si>
+  <si>
+    <t>Had a very bad dream which affected my whole day</t>
+  </si>
+  <si>
+    <t>Took my mother to a dentist</t>
   </si>
 </sst>
 </file>
@@ -2052,49 +2058,97 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B27" s="14">
+        <v>480</v>
+      </c>
+      <c r="C27" s="14">
+        <v>30</v>
+      </c>
+      <c r="D27" s="14">
+        <v>60</v>
+      </c>
+      <c r="E27" s="14">
+        <v>15</v>
+      </c>
+      <c r="F27" s="14">
+        <v>250</v>
+      </c>
+      <c r="G27" s="14">
+        <v>5</v>
+      </c>
+      <c r="H27" s="14">
+        <v>300</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1135</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>305</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14">
+        <v>60</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
+        <v>150</v>
+      </c>
+      <c r="G28" s="14">
+        <v>3</v>
+      </c>
+      <c r="H28" s="14">
+        <v>240</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB75F44F-1C27-4EDB-ADB7-956E39346965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFFCE00E-46CF-4758-8095-F3ECC283819C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -38,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -291,6 +288,18 @@
   <si>
     <t>Took my mother to a dentist</t>
   </si>
+  <si>
+    <t>Had to visit the election support office and get my voter card made</t>
+  </si>
+  <si>
+    <t>Met a friend and had breakfast and lunch together</t>
+  </si>
+  <si>
+    <t>Got my car's issues resolved like headlights and ac</t>
+  </si>
+  <si>
+    <t>Went to run an errand in my neighbouring city for my father's business</t>
+  </si>
 </sst>
 </file>
 
@@ -299,7 +308,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -380,6 +389,13 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -428,7 +444,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -472,35 +488,23 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2150,93 +2154,181 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+    <row r="29" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="21">
+        <v>46276</v>
+      </c>
+      <c r="B29" s="22">
+        <v>480</v>
+      </c>
+      <c r="C29" s="22">
+        <v>30</v>
+      </c>
+      <c r="D29" s="22">
+        <v>30</v>
+      </c>
+      <c r="E29" s="22">
+        <v>20</v>
+      </c>
+      <c r="F29" s="22">
+        <v>150</v>
+      </c>
+      <c r="G29" s="22">
+        <v>3</v>
+      </c>
+      <c r="H29" s="22">
+        <v>360</v>
+      </c>
+      <c r="I29" s="23">
+        <v>1070</v>
+      </c>
+      <c r="J29" s="23">
+        <v>370</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="L29" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="21">
+        <v>46277</v>
+      </c>
+      <c r="B30" s="22">
+        <v>300</v>
+      </c>
+      <c r="C30" s="22">
+        <v>0</v>
+      </c>
+      <c r="D30" s="22">
+        <v>0</v>
+      </c>
+      <c r="E30" s="22">
+        <v>0</v>
+      </c>
+      <c r="F30" s="22">
+        <v>0</v>
+      </c>
+      <c r="G30" s="22">
+        <v>0</v>
+      </c>
+      <c r="H30" s="22">
+        <v>480</v>
+      </c>
+      <c r="I30" s="23">
+        <v>780</v>
+      </c>
+      <c r="J30" s="23">
+        <v>660</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="L30" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="M30" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="N30" s="24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="21">
+        <v>46278</v>
+      </c>
+      <c r="B31" s="22">
+        <v>360</v>
+      </c>
+      <c r="C31" s="22">
+        <v>60</v>
+      </c>
+      <c r="D31" s="22">
+        <v>60</v>
+      </c>
+      <c r="E31" s="22">
+        <v>30</v>
+      </c>
+      <c r="F31" s="22">
+        <v>0</v>
+      </c>
+      <c r="G31" s="22">
+        <v>0</v>
+      </c>
+      <c r="H31" s="22">
+        <v>360</v>
+      </c>
+      <c r="I31" s="23">
+        <v>870</v>
+      </c>
+      <c r="J31" s="23">
+        <v>570</v>
+      </c>
+      <c r="K31" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="L31" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="M31" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="N31" s="24" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="21">
+        <v>46279</v>
+      </c>
+      <c r="B32" s="22">
+        <v>360</v>
+      </c>
+      <c r="C32" s="22">
+        <v>30</v>
+      </c>
+      <c r="D32" s="22">
+        <v>30</v>
+      </c>
+      <c r="E32" s="22">
+        <v>0</v>
+      </c>
+      <c r="F32" s="22">
+        <v>200</v>
+      </c>
+      <c r="G32" s="22">
+        <v>4</v>
+      </c>
+      <c r="H32" s="22">
+        <v>300</v>
+      </c>
+      <c r="I32" s="23">
+        <v>920</v>
+      </c>
+      <c r="J32" s="23">
+        <v>520</v>
+      </c>
+      <c r="K32" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="L32" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="N32" s="24" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>
@@ -10365,31 +10457,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J13:J401">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J7 J9:J12">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J8">
+  <conditionalFormatting sqref="J6:J28 J33:J401">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K28 K33:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L28 L33:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M28 M33:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\Downloads\CAP776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFFCE00E-46CF-4758-8095-F3ECC283819C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D238B1E-803E-4819-8D1F-43ECCFD7B37C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -300,6 +300,9 @@
   <si>
     <t>Went to run an errand in my neighbouring city for my father's business</t>
   </si>
+  <si>
+    <t>Went to amritsar(Diago rooftop bar) to celeberate y friend's birthday</t>
+  </si>
 </sst>
 </file>
 
@@ -485,9 +488,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -500,6 +500,9 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -983,74 +986,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="24">
         <v>12610630</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="24"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="24"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -2155,202 +2158,226 @@
       </c>
     </row>
     <row r="29" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="21">
+      <c r="A29" s="18">
         <v>46276</v>
       </c>
-      <c r="B29" s="22">
+      <c r="B29" s="19">
         <v>480</v>
       </c>
-      <c r="C29" s="22">
+      <c r="C29" s="19">
         <v>30</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="19">
         <v>30</v>
       </c>
-      <c r="E29" s="22">
+      <c r="E29" s="19">
         <v>20</v>
       </c>
-      <c r="F29" s="22">
+      <c r="F29" s="19">
         <v>150</v>
       </c>
-      <c r="G29" s="22">
+      <c r="G29" s="19">
         <v>3</v>
       </c>
-      <c r="H29" s="22">
+      <c r="H29" s="19">
         <v>360</v>
       </c>
-      <c r="I29" s="23">
+      <c r="I29" s="20">
         <v>1070</v>
       </c>
-      <c r="J29" s="23">
+      <c r="J29" s="20">
         <v>370</v>
       </c>
-      <c r="K29" s="22" t="s">
+      <c r="K29" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="L29" s="22" t="s">
+      <c r="L29" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="M29" s="22" t="s">
+      <c r="M29" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="N29" s="24" t="s">
+      <c r="N29" s="21" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="21">
+      <c r="A30" s="18">
         <v>46277</v>
       </c>
-      <c r="B30" s="22">
+      <c r="B30" s="19">
         <v>300</v>
       </c>
-      <c r="C30" s="22">
+      <c r="C30" s="19">
         <v>0</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="19">
         <v>0</v>
       </c>
-      <c r="E30" s="22">
+      <c r="E30" s="19">
         <v>0</v>
       </c>
-      <c r="F30" s="22">
+      <c r="F30" s="19">
         <v>0</v>
       </c>
-      <c r="G30" s="22">
+      <c r="G30" s="19">
         <v>0</v>
       </c>
-      <c r="H30" s="22">
+      <c r="H30" s="19">
         <v>480</v>
       </c>
-      <c r="I30" s="23">
+      <c r="I30" s="20">
         <v>780</v>
       </c>
-      <c r="J30" s="23">
+      <c r="J30" s="20">
         <v>660</v>
       </c>
-      <c r="K30" s="22" t="s">
+      <c r="K30" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="L30" s="22" t="s">
+      <c r="L30" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="M30" s="22" t="s">
+      <c r="M30" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="N30" s="24" t="s">
+      <c r="N30" s="21" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="21">
+      <c r="A31" s="18">
         <v>46278</v>
       </c>
-      <c r="B31" s="22">
+      <c r="B31" s="19">
         <v>360</v>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="19">
         <v>60</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="19">
         <v>60</v>
       </c>
-      <c r="E31" s="22">
+      <c r="E31" s="19">
         <v>30</v>
       </c>
-      <c r="F31" s="22">
+      <c r="F31" s="19">
         <v>0</v>
       </c>
-      <c r="G31" s="22">
+      <c r="G31" s="19">
         <v>0</v>
       </c>
-      <c r="H31" s="22">
+      <c r="H31" s="19">
         <v>360</v>
       </c>
-      <c r="I31" s="23">
+      <c r="I31" s="20">
         <v>870</v>
       </c>
-      <c r="J31" s="23">
+      <c r="J31" s="20">
         <v>570</v>
       </c>
-      <c r="K31" s="22" t="s">
+      <c r="K31" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="L31" s="22" t="s">
+      <c r="L31" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="M31" s="22" t="s">
+      <c r="M31" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="N31" s="24" t="s">
+      <c r="N31" s="21" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="21">
+      <c r="A32" s="18">
         <v>46279</v>
       </c>
-      <c r="B32" s="22">
+      <c r="B32" s="19">
         <v>360</v>
       </c>
-      <c r="C32" s="22">
+      <c r="C32" s="19">
         <v>30</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="19">
         <v>30</v>
       </c>
-      <c r="E32" s="22">
+      <c r="E32" s="19">
         <v>0</v>
       </c>
-      <c r="F32" s="22">
+      <c r="F32" s="19">
         <v>200</v>
       </c>
-      <c r="G32" s="22">
+      <c r="G32" s="19">
         <v>4</v>
       </c>
-      <c r="H32" s="22">
+      <c r="H32" s="19">
         <v>300</v>
       </c>
-      <c r="I32" s="23">
+      <c r="I32" s="20">
         <v>920</v>
       </c>
-      <c r="J32" s="23">
+      <c r="J32" s="20">
         <v>520</v>
       </c>
-      <c r="K32" s="22" t="s">
+      <c r="K32" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="L32" s="22" t="s">
+      <c r="L32" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="M32" s="22" t="s">
+      <c r="M32" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="N32" s="24" t="s">
+      <c r="N32" s="21" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+    <row r="33" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A33" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B33" s="14">
+        <v>420</v>
+      </c>
+      <c r="C33" s="14">
+        <v>30</v>
+      </c>
+      <c r="D33" s="14">
+        <v>30</v>
+      </c>
+      <c r="E33" s="14">
+        <v>60</v>
+      </c>
+      <c r="F33" s="14">
+        <v>300</v>
+      </c>
+      <c r="G33" s="14">
+        <v>6</v>
+      </c>
+      <c r="H33" s="14">
+        <v>300</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>
@@ -10477,6 +10504,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D238B1E-803E-4819-8D1F-43ECCFD7B37C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C32CEAA5-47D9-4FB7-A1B1-11E593F64921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,15 @@
   </si>
   <si>
     <t>Went to amritsar(Diago rooftop bar) to celeberate y friend's birthday</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Was at college for most of the day and performed volunatiry service at temple</t>
+  </si>
+  <si>
+    <t>Went to see a movie " Hanuman-ansh" with my family and family friends</t>
   </si>
 </sst>
 </file>
@@ -2379,52 +2388,102 @@
         <v>88</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+    <row r="34" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B34" s="14">
+        <v>360</v>
+      </c>
+      <c r="C34" s="14">
+        <v>30</v>
+      </c>
+      <c r="D34" s="14">
+        <v>60</v>
+      </c>
+      <c r="E34" s="14">
+        <v>30</v>
+      </c>
+      <c r="F34" s="14">
+        <v>350</v>
+      </c>
+      <c r="G34" s="14">
+        <v>7</v>
+      </c>
+      <c r="H34" s="14">
+        <v>240</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+        <v>370</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B35" s="14">
+        <v>420</v>
+      </c>
+      <c r="C35" s="14">
+        <v>0</v>
+      </c>
+      <c r="D35" s="14">
+        <v>30</v>
+      </c>
+      <c r="E35" s="14">
+        <v>30</v>
+      </c>
+      <c r="F35" s="14">
+        <v>200</v>
+      </c>
+      <c r="G35" s="14">
+        <v>4</v>
+      </c>
+      <c r="H35" s="14">
+        <v>300</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
+      <c r="A36" s="13">
+        <v>46283</v>
+      </c>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
       <c r="D36" s="14"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C32CEAA5-47D9-4FB7-A1B1-11E593F64921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03506ED2-FFE8-4126-98BF-C25CFDA24539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -311,6 +311,15 @@
   </si>
   <si>
     <t>Went to see a movie " Hanuman-ansh" with my family and family friends</t>
+  </si>
+  <si>
+    <t>Didn't sleep much so was feeling sleepy the whole day</t>
+  </si>
+  <si>
+    <t>Had to visit college for an hour to give my CA and later me and my father had a breakfast meeting with a potential client</t>
+  </si>
+  <si>
+    <t>Stayed home and rested for Sunday</t>
   </si>
 </sst>
 </file>
@@ -2480,73 +2489,143 @@
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="13">
         <v>46283</v>
       </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="B36" s="14">
+        <v>180</v>
+      </c>
+      <c r="C36" s="14">
+        <v>30</v>
+      </c>
+      <c r="D36" s="14">
+        <v>60</v>
+      </c>
+      <c r="E36" s="14">
+        <v>0</v>
+      </c>
+      <c r="F36" s="14">
+        <v>200</v>
+      </c>
+      <c r="G36" s="14">
+        <v>4</v>
+      </c>
+      <c r="H36" s="14">
+        <v>360</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+        <v>610</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B37" s="14">
+        <v>420</v>
+      </c>
+      <c r="C37" s="14">
+        <v>0</v>
+      </c>
+      <c r="D37" s="14">
+        <v>120</v>
+      </c>
+      <c r="E37" s="14">
+        <v>15</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>420</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>975</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+        <v>465</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B38" s="14">
+        <v>360</v>
+      </c>
+      <c r="C38" s="14">
+        <v>0</v>
+      </c>
+      <c r="D38" s="14">
+        <v>120</v>
+      </c>
+      <c r="E38" s="14">
+        <v>0</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>200</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>760</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03506ED2-FFE8-4126-98BF-C25CFDA24539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C528955-EC19-4ACC-B3C4-D990B0FEC20E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t>Stayed home and rested for Sunday</t>
+  </si>
+  <si>
+    <t>Just like a regular Tuesday, visited temple for voluntary service</t>
   </si>
 </sst>
 </file>
@@ -2628,48 +2631,93 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B39" s="14">
+        <v>480</v>
+      </c>
+      <c r="C39" s="14">
+        <v>30</v>
+      </c>
+      <c r="D39" s="14">
+        <v>60</v>
+      </c>
+      <c r="E39" s="14">
+        <v>0</v>
+      </c>
+      <c r="F39" s="14">
+        <v>250</v>
+      </c>
+      <c r="G39" s="14">
+        <v>5</v>
+      </c>
+      <c r="H39" s="14">
+        <v>360</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+        <v>260</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A40" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B40" s="14">
+        <v>420</v>
+      </c>
+      <c r="C40" s="14">
+        <v>0</v>
+      </c>
+      <c r="D40" s="14">
+        <v>60</v>
+      </c>
+      <c r="E40" s="14">
+        <v>0</v>
+      </c>
+      <c r="F40" s="14">
+        <v>350</v>
+      </c>
+      <c r="G40" s="14">
+        <v>7</v>
+      </c>
+      <c r="H40" s="14">
+        <v>240</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>1070</v>
+      </c>
+      <c r="J40" s="15"/>
+      <c r="K40" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C528955-EC19-4ACC-B3C4-D990B0FEC20E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4261DA0-0A56-4731-8F98-A4D670AF72C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2702,10 +2702,11 @@
         <v>240</v>
       </c>
       <c r="I40" s="15">
-        <f t="shared" si="2"/>
         <v>1070</v>
       </c>
-      <c r="J40" s="15"/>
+      <c r="J40" s="15">
+        <v>370</v>
+      </c>
       <c r="K40" s="16" t="s">
         <v>53</v>
       </c>
@@ -2728,14 +2729,8 @@
       <c r="F41" s="14"/>
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
       <c r="K41" s="16"/>
       <c r="L41" s="16"/>
       <c r="M41" s="16"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4261DA0-0A56-4731-8F98-A4D670AF72C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FCF2E5-4C1B-40B6-869E-8C195C232BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -323,6 +323,15 @@
   </si>
   <si>
     <t>Just like a regular Tuesday, visited temple for voluntary service</t>
+  </si>
+  <si>
+    <t>Cleaned my car myself with the new wash kit I ordered</t>
+  </si>
+  <si>
+    <t>Was at my shop and spent most of the day there due to my dad being out for business</t>
+  </si>
+  <si>
+    <t>Had our colony meeting regarding installing a new gate in colony and spent most of my day in this issue only</t>
   </si>
 </sst>
 </file>
@@ -2721,86 +2730,182 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
+      <c r="A41" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B41" s="14">
+        <v>360</v>
+      </c>
+      <c r="C41" s="14">
+        <v>60</v>
+      </c>
+      <c r="D41" s="14">
+        <v>30</v>
+      </c>
+      <c r="E41" s="14">
+        <v>0</v>
+      </c>
+      <c r="F41" s="14">
+        <v>350</v>
+      </c>
+      <c r="G41" s="14">
+        <v>7</v>
+      </c>
+      <c r="H41" s="14">
+        <v>120</v>
+      </c>
       <c r="I41" s="15"/>
       <c r="J41" s="15"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B42" s="14">
+        <v>420</v>
+      </c>
+      <c r="C42" s="14">
+        <v>30</v>
+      </c>
+      <c r="D42" s="14">
+        <v>120</v>
+      </c>
+      <c r="E42" s="14">
+        <v>30</v>
+      </c>
+      <c r="F42" s="14">
+        <v>200</v>
+      </c>
+      <c r="G42" s="14">
+        <v>4</v>
+      </c>
+      <c r="H42" s="14">
+        <v>240</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+        <v>400</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B43" s="14">
+        <v>480</v>
+      </c>
+      <c r="C43" s="14">
+        <v>0</v>
+      </c>
+      <c r="D43" s="14">
+        <v>30</v>
+      </c>
+      <c r="E43" s="14">
+        <v>0</v>
+      </c>
+      <c r="F43" s="14">
+        <v>100</v>
+      </c>
+      <c r="G43" s="14">
+        <v>2</v>
+      </c>
+      <c r="H43" s="14">
+        <v>360</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+        <v>470</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B44" s="14">
+        <v>420</v>
+      </c>
+      <c r="C44" s="14">
+        <v>30</v>
+      </c>
+      <c r="D44" s="14">
+        <v>0</v>
+      </c>
+      <c r="E44" s="14">
+        <v>60</v>
+      </c>
+      <c r="F44" s="14">
+        <v>150</v>
+      </c>
+      <c r="G44" s="14">
+        <v>3</v>
+      </c>
+      <c r="H44" s="14">
+        <v>240</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FCF2E5-4C1B-40B6-869E-8C195C232BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{678B46CE-F56A-46BF-8FE5-D0A0A1B1ECF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -332,6 +332,12 @@
   </si>
   <si>
     <t>Had our colony meeting regarding installing a new gate in colony and spent most of my day in this issue only</t>
+  </si>
+  <si>
+    <t>Travelled with family to chintpurni city to visit the famous chintpurni mata temple</t>
+  </si>
+  <si>
+    <t>Was sleepy and tired due to extensive travelling the day before</t>
   </si>
 </sst>
 </file>
@@ -2907,49 +2913,97 @@
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+    <row r="45" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A45" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B45" s="14">
+        <v>360</v>
+      </c>
+      <c r="C45" s="14">
+        <v>0</v>
+      </c>
+      <c r="D45" s="14">
+        <v>0</v>
+      </c>
+      <c r="E45" s="14">
+        <v>0</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>0</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>360</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A46" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B46" s="14">
+        <v>540</v>
+      </c>
+      <c r="C46" s="14">
+        <v>0</v>
+      </c>
+      <c r="D46" s="14">
+        <v>180</v>
+      </c>
+      <c r="E46" s="14">
+        <v>0</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>240</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{678B46CE-F56A-46BF-8FE5-D0A0A1B1ECF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D74B43-F8DE-4B02-BB64-B0394B63405F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -338,6 +338,15 @@
   </si>
   <si>
     <t>Was sleepy and tired due to extensive travelling the day before</t>
+  </si>
+  <si>
+    <t>As a regular Tuesday, went to our nearby temple and did voluntary service there</t>
+  </si>
+  <si>
+    <t>2026-09030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgaded our shop's CCTV and was mostly busy managing labour that day </t>
   </si>
 </sst>
 </file>
@@ -3005,49 +3014,97 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+    <row r="47" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A47" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B47" s="14">
+        <v>420</v>
+      </c>
+      <c r="C47" s="14">
+        <v>30</v>
+      </c>
+      <c r="D47" s="14">
+        <v>120</v>
+      </c>
+      <c r="E47" s="14">
+        <v>30</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>360</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+        <v>480</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A48" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B48" s="14">
+        <v>360</v>
+      </c>
+      <c r="C48" s="14">
+        <v>0</v>
+      </c>
+      <c r="D48" s="14">
+        <v>240</v>
+      </c>
+      <c r="E48" s="14">
+        <v>0</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>240</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>600</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D74B43-F8DE-4B02-BB64-B0394B63405F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A901607-2258-428D-BB5E-CDD8EBF37443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,15 +27,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="118">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -343,10 +340,52 @@
     <t>As a regular Tuesday, went to our nearby temple and did voluntary service there</t>
   </si>
   <si>
-    <t>2026-09030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upgaded our shop's CCTV and was mostly busy managing labour that day </t>
+    <t>Upgaded our shop's CCTV and was mostly busy managing labour that day</t>
+  </si>
+  <si>
+    <t>Had a family dinner at home as some relatives came over to visit us</t>
+  </si>
+  <si>
+    <t>Visited our warehouse with my father and checked the stock and inventory</t>
+  </si>
+  <si>
+    <t>Went to temple for voluntary service</t>
+  </si>
+  <si>
+    <t>Laptop's charger stopped working</t>
+  </si>
+  <si>
+    <t>Got the whole laptop replaced as only bought it 2 days ago</t>
+  </si>
+  <si>
+    <t>Bought a new laptop - HP Victus</t>
+  </si>
+  <si>
+    <t>Prepared whole day for next mid term</t>
+  </si>
+  <si>
+    <t>Spent the afternoon at home with family</t>
+  </si>
+  <si>
+    <t>Spent most of the day completing college assignments</t>
+  </si>
+  <si>
+    <t>Took my car to get the headlights replaced</t>
+  </si>
+  <si>
+    <t>had Dinner with friends after a long time</t>
+  </si>
+  <si>
+    <t>Went to nearby temple for some voulntary service</t>
+  </si>
+  <si>
+    <t>Visited the local market to purchase some items for shop</t>
+  </si>
+  <si>
+    <t>Met an old friend and hanged out</t>
+  </si>
+  <si>
+    <t>Helped workers at my shop with some maintanence work</t>
   </si>
 </sst>
 </file>
@@ -356,13 +395,20 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -465,7 +511,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -488,34 +534,81 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -524,7 +617,7 @@
     <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -533,24 +626,30 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{6AAC06E2-4899-49C7-908B-705B9F73022A}"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -634,6 +733,9 @@
       <rgbColor rgb="00333399"/>
       <rgbColor rgb="00333333"/>
     </indexedColors>
+    <mruColors>
+      <color rgb="FFFFFF66"/>
+    </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1055,15 +1157,15 @@
       <c r="B2" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="26"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F2" s="24">
         <v>12610630</v>
       </c>
-      <c r="G2" s="24"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -1072,15 +1174,15 @@
       <c r="B3" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="26"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="G3" s="24"/>
+      <c r="G3" s="26"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
@@ -2810,11 +2912,9 @@
         <v>240</v>
       </c>
       <c r="I42" s="15">
-        <f t="shared" si="2"/>
         <v>1040</v>
       </c>
       <c r="J42" s="15">
-        <f t="shared" si="3"/>
         <v>400</v>
       </c>
       <c r="K42" s="16" t="s">
@@ -2856,11 +2956,9 @@
         <v>360</v>
       </c>
       <c r="I43" s="15">
-        <f t="shared" si="2"/>
         <v>970</v>
       </c>
       <c r="J43" s="15">
-        <f t="shared" si="3"/>
         <v>470</v>
       </c>
       <c r="K43" s="16" t="s">
@@ -2902,11 +3000,9 @@
         <v>240</v>
       </c>
       <c r="I44" s="15">
-        <f t="shared" si="2"/>
         <v>900</v>
       </c>
       <c r="J44" s="15">
-        <f t="shared" si="3"/>
         <v>540</v>
       </c>
       <c r="K44" s="16" t="s">
@@ -2948,11 +3044,9 @@
         <v>0</v>
       </c>
       <c r="I45" s="15">
-        <f t="shared" si="2"/>
         <v>360</v>
       </c>
       <c r="J45" s="15">
-        <f t="shared" si="3"/>
         <v>1080</v>
       </c>
       <c r="K45" s="16" t="s">
@@ -2972,45 +3066,43 @@
       <c r="A46" s="13">
         <v>46293</v>
       </c>
-      <c r="B46" s="14">
+      <c r="B46" s="27">
         <v>540</v>
       </c>
-      <c r="C46" s="14">
-        <v>0</v>
-      </c>
-      <c r="D46" s="14">
+      <c r="C46" s="27">
+        <v>0</v>
+      </c>
+      <c r="D46" s="27">
         <v>180</v>
       </c>
-      <c r="E46" s="14">
-        <v>0</v>
-      </c>
-      <c r="F46" s="14">
-        <v>0</v>
-      </c>
-      <c r="G46" s="14">
-        <v>0</v>
-      </c>
-      <c r="H46" s="14">
+      <c r="E46" s="27">
+        <v>0</v>
+      </c>
+      <c r="F46" s="27">
+        <v>0</v>
+      </c>
+      <c r="G46" s="27">
+        <v>0</v>
+      </c>
+      <c r="H46" s="27">
         <v>240</v>
       </c>
       <c r="I46" s="15">
-        <f t="shared" si="2"/>
         <v>960</v>
       </c>
       <c r="J46" s="15">
-        <f t="shared" si="3"/>
         <v>480</v>
       </c>
-      <c r="K46" s="16" t="s">
+      <c r="K46" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="L46" s="16" t="s">
+      <c r="L46" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="M46" s="16" t="s">
+      <c r="M46" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="N46" s="17" t="s">
+      <c r="N46" s="13" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3018,555 +3110,1055 @@
       <c r="A47" s="13">
         <v>46294</v>
       </c>
-      <c r="B47" s="14">
+      <c r="B47" s="27">
         <v>420</v>
       </c>
-      <c r="C47" s="14">
+      <c r="C47" s="27">
         <v>30</v>
       </c>
-      <c r="D47" s="14">
+      <c r="D47" s="27">
         <v>120</v>
       </c>
-      <c r="E47" s="14">
+      <c r="E47" s="27">
         <v>30</v>
       </c>
-      <c r="F47" s="14">
-        <v>0</v>
-      </c>
-      <c r="G47" s="14">
-        <v>0</v>
-      </c>
-      <c r="H47" s="14">
+      <c r="F47" s="27">
+        <v>0</v>
+      </c>
+      <c r="G47" s="27">
+        <v>0</v>
+      </c>
+      <c r="H47" s="27">
         <v>360</v>
       </c>
       <c r="I47" s="15">
+        <v>960</v>
+      </c>
+      <c r="J47" s="15">
+        <v>480</v>
+      </c>
+      <c r="K47" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="L47" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="M47" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A48" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B48" s="27">
+        <v>360</v>
+      </c>
+      <c r="C48" s="27">
+        <v>0</v>
+      </c>
+      <c r="D48" s="27">
+        <v>240</v>
+      </c>
+      <c r="E48" s="27">
+        <v>0</v>
+      </c>
+      <c r="F48" s="27">
+        <v>0</v>
+      </c>
+      <c r="G48" s="27">
+        <v>0</v>
+      </c>
+      <c r="H48" s="27">
+        <v>240</v>
+      </c>
+      <c r="I48" s="15">
+        <v>840</v>
+      </c>
+      <c r="J48" s="15">
+        <v>600</v>
+      </c>
+      <c r="K48" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="N48" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A49" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B49" s="14">
+        <v>420</v>
+      </c>
+      <c r="C49" s="14">
+        <v>120</v>
+      </c>
+      <c r="D49" s="14">
+        <v>120</v>
+      </c>
+      <c r="E49" s="14">
+        <v>30</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>120</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="2"/>
-        <v>960</v>
-      </c>
-      <c r="J47" s="15">
+        <v>810</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="3"/>
+        <v>630</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B50" s="14">
+        <v>360</v>
+      </c>
+      <c r="C50" s="14">
+        <v>0</v>
+      </c>
+      <c r="D50" s="14">
+        <v>0</v>
+      </c>
+      <c r="E50" s="14">
+        <v>0</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>360</v>
+      </c>
+      <c r="I50" s="15">
+        <f t="shared" si="2"/>
+        <v>720</v>
+      </c>
+      <c r="J50" s="15">
+        <f t="shared" si="3"/>
+        <v>720</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B51" s="14">
+        <v>400</v>
+      </c>
+      <c r="C51" s="14">
+        <v>60</v>
+      </c>
+      <c r="D51" s="14">
+        <v>120</v>
+      </c>
+      <c r="E51" s="14">
+        <v>30</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>360</v>
+      </c>
+      <c r="I51" s="15">
+        <f t="shared" si="2"/>
+        <v>970</v>
+      </c>
+      <c r="J51" s="15">
+        <f t="shared" si="3"/>
+        <v>470</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B52" s="14">
+        <v>240</v>
+      </c>
+      <c r="C52" s="14">
+        <v>60</v>
+      </c>
+      <c r="D52" s="14">
+        <v>60</v>
+      </c>
+      <c r="E52" s="14">
+        <v>30</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>420</v>
+      </c>
+      <c r="I52" s="15">
+        <f t="shared" si="2"/>
+        <v>810</v>
+      </c>
+      <c r="J52" s="15">
+        <f t="shared" si="3"/>
+        <v>630</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B53" s="14">
+        <v>420</v>
+      </c>
+      <c r="C53" s="14">
+        <v>60</v>
+      </c>
+      <c r="D53" s="14">
+        <v>240</v>
+      </c>
+      <c r="E53" s="14">
+        <v>0</v>
+      </c>
+      <c r="F53" s="14">
+        <v>300</v>
+      </c>
+      <c r="G53" s="14">
+        <v>6</v>
+      </c>
+      <c r="H53" s="14">
+        <v>120</v>
+      </c>
+      <c r="I53" s="15">
+        <f t="shared" si="2"/>
+        <v>1140</v>
+      </c>
+      <c r="J53" s="15">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B54" s="14">
         <v>480</v>
       </c>
-      <c r="K47" s="16" t="s">
+      <c r="C54" s="14">
+        <v>0</v>
+      </c>
+      <c r="D54" s="14">
+        <v>30</v>
+      </c>
+      <c r="E54" s="14">
+        <v>20</v>
+      </c>
+      <c r="F54" s="14">
+        <v>350</v>
+      </c>
+      <c r="G54" s="14">
+        <v>7</v>
+      </c>
+      <c r="H54" s="14">
+        <v>240</v>
+      </c>
+      <c r="I54" s="15">
+        <f t="shared" si="2"/>
+        <v>1120</v>
+      </c>
+      <c r="J54" s="15">
+        <f t="shared" si="3"/>
+        <v>320</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B55" s="14">
+        <v>480</v>
+      </c>
+      <c r="C55" s="14">
+        <v>0</v>
+      </c>
+      <c r="D55" s="14">
+        <v>0</v>
+      </c>
+      <c r="E55" s="14">
+        <v>20</v>
+      </c>
+      <c r="F55" s="14">
+        <v>350</v>
+      </c>
+      <c r="G55" s="14">
+        <v>7</v>
+      </c>
+      <c r="H55" s="14">
+        <v>180</v>
+      </c>
+      <c r="I55" s="15">
+        <f t="shared" si="2"/>
+        <v>1030</v>
+      </c>
+      <c r="J55" s="15">
+        <f t="shared" si="3"/>
+        <v>410</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B56" s="14">
+        <v>360</v>
+      </c>
+      <c r="C56" s="14">
+        <v>0</v>
+      </c>
+      <c r="D56" s="14">
+        <v>120</v>
+      </c>
+      <c r="E56" s="14">
+        <v>30</v>
+      </c>
+      <c r="F56" s="14">
+        <v>200</v>
+      </c>
+      <c r="G56" s="14">
+        <v>4</v>
+      </c>
+      <c r="H56" s="14">
+        <v>180</v>
+      </c>
+      <c r="I56" s="15">
+        <f t="shared" si="2"/>
+        <v>890</v>
+      </c>
+      <c r="J56" s="15">
+        <f t="shared" si="3"/>
+        <v>550</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A57" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B57" s="14">
+        <v>480</v>
+      </c>
+      <c r="C57" s="14">
+        <v>30</v>
+      </c>
+      <c r="D57" s="14">
+        <v>180</v>
+      </c>
+      <c r="E57" s="14">
+        <v>0</v>
+      </c>
+      <c r="F57" s="14">
+        <v>200</v>
+      </c>
+      <c r="G57" s="14">
+        <v>4</v>
+      </c>
+      <c r="H57" s="14">
+        <v>300</v>
+      </c>
+      <c r="I57" s="15">
+        <f t="shared" si="2"/>
+        <v>1190</v>
+      </c>
+      <c r="J57" s="15">
+        <f t="shared" si="3"/>
+        <v>250</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A58" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B58" s="14">
+        <v>420</v>
+      </c>
+      <c r="C58" s="14">
+        <v>120</v>
+      </c>
+      <c r="D58" s="14">
+        <v>20</v>
+      </c>
+      <c r="E58" s="14">
+        <v>0</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>360</v>
+      </c>
+      <c r="I58" s="15">
+        <f t="shared" si="2"/>
+        <v>920</v>
+      </c>
+      <c r="J58" s="15">
+        <f t="shared" si="3"/>
+        <v>520</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B59" s="14">
+        <v>360</v>
+      </c>
+      <c r="C59" s="14">
+        <v>60</v>
+      </c>
+      <c r="D59" s="14">
+        <v>0</v>
+      </c>
+      <c r="E59" s="14">
+        <v>0</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>300</v>
+      </c>
+      <c r="I59" s="15">
+        <f t="shared" si="2"/>
+        <v>720</v>
+      </c>
+      <c r="J59" s="15">
+        <f t="shared" si="3"/>
+        <v>720</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B60" s="14">
+        <v>420</v>
+      </c>
+      <c r="C60" s="14">
+        <v>40</v>
+      </c>
+      <c r="D60" s="14">
+        <v>30</v>
+      </c>
+      <c r="E60" s="14">
+        <v>0</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>240</v>
+      </c>
+      <c r="I60" s="15">
+        <f t="shared" si="2"/>
+        <v>730</v>
+      </c>
+      <c r="J60" s="15">
+        <f t="shared" si="3"/>
+        <v>710</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A61" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B61" s="14">
+        <v>300</v>
+      </c>
+      <c r="C61" s="14">
+        <v>0</v>
+      </c>
+      <c r="D61" s="14">
+        <v>60</v>
+      </c>
+      <c r="E61" s="14">
+        <v>30</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>480</v>
+      </c>
+      <c r="I61" s="15">
+        <f t="shared" si="2"/>
+        <v>870</v>
+      </c>
+      <c r="J61" s="15">
+        <f t="shared" si="3"/>
+        <v>570</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B62" s="14">
+        <v>360</v>
+      </c>
+      <c r="C62" s="14">
+        <v>0</v>
+      </c>
+      <c r="D62" s="14">
+        <v>60</v>
+      </c>
+      <c r="E62" s="14">
+        <v>20</v>
+      </c>
+      <c r="F62" s="14">
+        <v>0</v>
+      </c>
+      <c r="G62" s="14">
+        <v>0</v>
+      </c>
+      <c r="H62" s="14">
+        <v>120</v>
+      </c>
+      <c r="I62" s="15">
+        <f t="shared" si="2"/>
+        <v>560</v>
+      </c>
+      <c r="J62" s="15">
+        <f t="shared" si="3"/>
+        <v>880</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B63" s="14">
+        <v>420</v>
+      </c>
+      <c r="C63" s="14">
+        <v>30</v>
+      </c>
+      <c r="D63" s="14">
+        <v>240</v>
+      </c>
+      <c r="E63" s="14">
+        <v>30</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>150</v>
+      </c>
+      <c r="I63" s="15">
+        <f t="shared" si="2"/>
+        <v>870</v>
+      </c>
+      <c r="J63" s="15">
+        <f t="shared" si="3"/>
+        <v>570</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A64" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B64" s="14">
+        <v>360</v>
+      </c>
+      <c r="C64" s="14">
+        <v>360</v>
+      </c>
+      <c r="D64" s="14">
+        <v>0</v>
+      </c>
+      <c r="E64" s="14">
+        <v>60</v>
+      </c>
+      <c r="F64" s="14">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14">
+        <v>240</v>
+      </c>
+      <c r="I64" s="15">
+        <f t="shared" si="2"/>
+        <v>1020</v>
+      </c>
+      <c r="J64" s="15">
+        <f t="shared" si="3"/>
+        <v>420</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B65" s="14">
+        <v>480</v>
+      </c>
+      <c r="C65" s="14">
+        <v>40</v>
+      </c>
+      <c r="D65" s="14">
+        <v>0</v>
+      </c>
+      <c r="E65" s="14">
+        <v>60</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>240</v>
+      </c>
+      <c r="I65" s="15">
+        <f t="shared" si="2"/>
+        <v>820</v>
+      </c>
+      <c r="J65" s="15">
+        <f t="shared" si="3"/>
+        <v>620</v>
+      </c>
+      <c r="K65" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="L47" s="16" t="s">
+      <c r="L65" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A66" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B66" s="14">
+        <v>480</v>
+      </c>
+      <c r="C66" s="14">
+        <v>120</v>
+      </c>
+      <c r="D66" s="14">
+        <v>120</v>
+      </c>
+      <c r="E66" s="14">
+        <v>30</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>480</v>
+      </c>
+      <c r="I66" s="15">
+        <f t="shared" si="2"/>
+        <v>1230</v>
+      </c>
+      <c r="J66" s="15">
+        <f t="shared" si="3"/>
+        <v>210</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N66" s="17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A67" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B67" s="14">
+        <v>420</v>
+      </c>
+      <c r="C67" s="14">
+        <v>45</v>
+      </c>
+      <c r="D67" s="14">
+        <v>60</v>
+      </c>
+      <c r="E67" s="14">
+        <v>120</v>
+      </c>
+      <c r="F67" s="14">
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>320</v>
+      </c>
+      <c r="I67" s="15">
+        <f t="shared" si="2"/>
+        <v>965</v>
+      </c>
+      <c r="J67" s="15">
+        <f t="shared" si="3"/>
+        <v>475</v>
+      </c>
+      <c r="K67" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="M47" s="16" t="s">
+      <c r="L67" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M67" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N47" s="17" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A48" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B48" s="14">
+      <c r="N67" s="17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A68" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B68" s="14">
+        <v>480</v>
+      </c>
+      <c r="C68" s="14">
+        <v>0</v>
+      </c>
+      <c r="D68" s="14">
+        <v>30</v>
+      </c>
+      <c r="E68" s="14">
+        <v>60</v>
+      </c>
+      <c r="F68" s="14">
+        <v>0</v>
+      </c>
+      <c r="G68" s="14">
+        <v>0</v>
+      </c>
+      <c r="H68" s="14">
+        <v>300</v>
+      </c>
+      <c r="I68" s="15">
+        <f t="shared" si="2"/>
+        <v>870</v>
+      </c>
+      <c r="J68" s="15">
+        <f t="shared" si="3"/>
+        <v>570</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N68" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A69" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B69" s="14">
         <v>360</v>
       </c>
-      <c r="C48" s="14">
-        <v>0</v>
-      </c>
-      <c r="D48" s="14">
+      <c r="C69" s="14">
+        <v>0</v>
+      </c>
+      <c r="D69" s="14">
+        <v>0</v>
+      </c>
+      <c r="E69" s="14">
+        <v>30</v>
+      </c>
+      <c r="F69" s="14">
+        <v>0</v>
+      </c>
+      <c r="G69" s="14">
+        <v>0</v>
+      </c>
+      <c r="H69" s="14">
         <v>240</v>
       </c>
-      <c r="E48" s="14">
-        <v>0</v>
-      </c>
-      <c r="F48" s="14">
-        <v>0</v>
-      </c>
-      <c r="G48" s="14">
-        <v>0</v>
-      </c>
-      <c r="H48" s="14">
-        <v>240</v>
-      </c>
-      <c r="I48" s="15">
+      <c r="I69" s="15">
         <f t="shared" si="2"/>
-        <v>840</v>
-      </c>
-      <c r="J48" s="15">
+        <v>630</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" si="3"/>
-        <v>600</v>
-      </c>
-      <c r="K48" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L48" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M48" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N48" s="17" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="17"/>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="17"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="17"/>
+        <v>810</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N69" s="17" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="13"/>
@@ -10881,21 +11473,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J28 J33:J401">
+  <conditionalFormatting sqref="J6:J28 J33:J44 J49:J401">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K28 K33:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K28 K33:K45 K49:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L28 L33:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L28 L33:L45 L49:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M28 M33:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M28 M33:M45 M49:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A901607-2258-428D-BB5E-CDD8EBF37443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033BD0A1-043F-4F43-B737-F577874151F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="119">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -386,6 +386,9 @@
   </si>
   <si>
     <t>Helped workers at my shop with some maintanence work</t>
+  </si>
+  <si>
+    <t>Had to urgently visit one of our relatives house, so missed all my classes for the day</t>
   </si>
 </sst>
 </file>
@@ -585,7 +588,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -643,9 +646,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3066,25 +3066,25 @@
       <c r="A46" s="13">
         <v>46293</v>
       </c>
-      <c r="B46" s="27">
+      <c r="B46" s="16">
         <v>540</v>
       </c>
-      <c r="C46" s="27">
-        <v>0</v>
-      </c>
-      <c r="D46" s="27">
+      <c r="C46" s="16">
+        <v>0</v>
+      </c>
+      <c r="D46" s="16">
         <v>180</v>
       </c>
-      <c r="E46" s="27">
-        <v>0</v>
-      </c>
-      <c r="F46" s="27">
-        <v>0</v>
-      </c>
-      <c r="G46" s="27">
-        <v>0</v>
-      </c>
-      <c r="H46" s="27">
+      <c r="E46" s="16">
+        <v>0</v>
+      </c>
+      <c r="F46" s="16">
+        <v>0</v>
+      </c>
+      <c r="G46" s="16">
+        <v>0</v>
+      </c>
+      <c r="H46" s="16">
         <v>240</v>
       </c>
       <c r="I46" s="15">
@@ -3110,25 +3110,25 @@
       <c r="A47" s="13">
         <v>46294</v>
       </c>
-      <c r="B47" s="27">
+      <c r="B47" s="16">
         <v>420</v>
       </c>
-      <c r="C47" s="27">
+      <c r="C47" s="16">
         <v>30</v>
       </c>
-      <c r="D47" s="27">
+      <c r="D47" s="16">
         <v>120</v>
       </c>
-      <c r="E47" s="27">
+      <c r="E47" s="16">
         <v>30</v>
       </c>
-      <c r="F47" s="27">
-        <v>0</v>
-      </c>
-      <c r="G47" s="27">
-        <v>0</v>
-      </c>
-      <c r="H47" s="27">
+      <c r="F47" s="16">
+        <v>0</v>
+      </c>
+      <c r="G47" s="16">
+        <v>0</v>
+      </c>
+      <c r="H47" s="16">
         <v>360</v>
       </c>
       <c r="I47" s="15">
@@ -3154,25 +3154,25 @@
       <c r="A48" s="13">
         <v>46295</v>
       </c>
-      <c r="B48" s="27">
+      <c r="B48" s="16">
         <v>360</v>
       </c>
-      <c r="C48" s="27">
-        <v>0</v>
-      </c>
-      <c r="D48" s="27">
+      <c r="C48" s="16">
+        <v>0</v>
+      </c>
+      <c r="D48" s="16">
         <v>240</v>
       </c>
-      <c r="E48" s="27">
-        <v>0</v>
-      </c>
-      <c r="F48" s="27">
-        <v>0</v>
-      </c>
-      <c r="G48" s="27">
-        <v>0</v>
-      </c>
-      <c r="H48" s="27">
+      <c r="E48" s="16">
+        <v>0</v>
+      </c>
+      <c r="F48" s="16">
+        <v>0</v>
+      </c>
+      <c r="G48" s="16">
+        <v>0</v>
+      </c>
+      <c r="H48" s="16">
         <v>240</v>
       </c>
       <c r="I48" s="15">
@@ -4161,70 +4161,142 @@
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="13"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
+      <c r="A70" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B70" s="14">
+        <v>360</v>
+      </c>
+      <c r="C70" s="14">
+        <v>30</v>
+      </c>
+      <c r="D70" s="14">
+        <v>120</v>
+      </c>
+      <c r="E70" s="14">
+        <v>0</v>
+      </c>
+      <c r="F70" s="14">
+        <v>150</v>
+      </c>
+      <c r="G70" s="14">
+        <v>3</v>
+      </c>
+      <c r="H70" s="14">
+        <v>320</v>
+      </c>
+      <c r="I70" s="15">
         <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-      <c r="N70" s="17"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="15" t="str">
+        <v>460</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N70" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A71" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B71" s="14">
+        <v>480</v>
+      </c>
+      <c r="C71" s="14">
+        <v>0</v>
+      </c>
+      <c r="D71" s="14">
+        <v>0</v>
+      </c>
+      <c r="E71" s="14">
+        <v>0</v>
+      </c>
+      <c r="F71" s="14">
+        <v>0</v>
+      </c>
+      <c r="G71" s="14">
+        <v>0</v>
+      </c>
+      <c r="H71" s="14">
+        <v>0</v>
+      </c>
+      <c r="I71" s="15">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>480</v>
+      </c>
+      <c r="J71" s="15">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
-      <c r="N71" s="17"/>
+        <v>960</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N71" s="17" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="15" t="str">
+      <c r="A72" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B72" s="14">
+        <v>600</v>
+      </c>
+      <c r="C72" s="14">
+        <v>120</v>
+      </c>
+      <c r="D72" s="14">
+        <v>0</v>
+      </c>
+      <c r="E72" s="14">
+        <v>0</v>
+      </c>
+      <c r="F72" s="14">
+        <v>0</v>
+      </c>
+      <c r="G72" s="14">
+        <v>0</v>
+      </c>
+      <c r="H72" s="14">
+        <v>0</v>
+      </c>
+      <c r="I72" s="15">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J72" s="15">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
-      <c r="N72" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N72" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="13"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033BD0A1-043F-4F43-B737-F577874151F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCCE2C15-3BD9-4A19-9ABF-E289681724C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="123">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -389,6 +389,18 @@
   </si>
   <si>
     <t>Had to urgently visit one of our relatives house, so missed all my classes for the day</t>
+  </si>
+  <si>
+    <t>was busy preparing my cousin's wedding</t>
+  </si>
+  <si>
+    <t>still busy at preparing for the cousin's wedding</t>
+  </si>
+  <si>
+    <t>attended my cousin's wedding</t>
+  </si>
+  <si>
+    <t>started a new book</t>
   </si>
 </sst>
 </file>
@@ -4298,93 +4310,189 @@
         <v>61</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="str">
+    <row r="73" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A73" s="13">
+        <v>46320</v>
+      </c>
+      <c r="B73" s="14">
+        <v>480</v>
+      </c>
+      <c r="C73" s="14">
+        <v>30</v>
+      </c>
+      <c r="D73" s="14">
+        <v>120</v>
+      </c>
+      <c r="E73" s="14">
+        <v>20</v>
+      </c>
+      <c r="F73" s="14">
+        <v>0</v>
+      </c>
+      <c r="G73" s="14">
+        <v>0</v>
+      </c>
+      <c r="H73" s="14">
+        <v>240</v>
+      </c>
+      <c r="I73" s="15">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J73" s="15">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
-      <c r="N73" s="17"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="15" t="str">
+        <v>550</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L73" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N73" s="17" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A74" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B74" s="14">
+        <v>180</v>
+      </c>
+      <c r="C74" s="14">
+        <v>30</v>
+      </c>
+      <c r="D74" s="14">
+        <v>0</v>
+      </c>
+      <c r="E74" s="14">
+        <v>20</v>
+      </c>
+      <c r="F74" s="14">
+        <v>0</v>
+      </c>
+      <c r="G74" s="14">
+        <v>0</v>
+      </c>
+      <c r="H74" s="14">
+        <v>240</v>
+      </c>
+      <c r="I74" s="15">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
+        <v>470</v>
+      </c>
+      <c r="J74" s="15">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
-      <c r="N74" s="17"/>
+        <v>970</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M74" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N74" s="17" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="13"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="15" t="str">
+      <c r="A75" s="13">
+        <v>39017</v>
+      </c>
+      <c r="B75" s="14">
+        <v>600</v>
+      </c>
+      <c r="C75" s="14">
+        <v>30</v>
+      </c>
+      <c r="D75" s="14">
+        <v>60</v>
+      </c>
+      <c r="E75" s="14">
+        <v>0</v>
+      </c>
+      <c r="F75" s="14">
+        <v>0</v>
+      </c>
+      <c r="G75" s="14">
+        <v>0</v>
+      </c>
+      <c r="H75" s="14">
+        <v>240</v>
+      </c>
+      <c r="I75" s="15">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J75" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J75" s="15">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
-      <c r="N75" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K75" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L75" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M75" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N75" s="17" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="13"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="15" t="str">
+      <c r="A76" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B76" s="14">
+        <v>540</v>
+      </c>
+      <c r="C76" s="14">
+        <v>0</v>
+      </c>
+      <c r="D76" s="14">
+        <v>240</v>
+      </c>
+      <c r="E76" s="14">
+        <v>0</v>
+      </c>
+      <c r="F76" s="14">
+        <v>350</v>
+      </c>
+      <c r="G76" s="14">
+        <v>7</v>
+      </c>
+      <c r="H76" s="14">
+        <v>180</v>
+      </c>
+      <c r="I76" s="15">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J76" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J76" s="15">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
-      <c r="N76" s="17"/>
+        <v>130</v>
+      </c>
+      <c r="K76" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L76" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M76" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N76" s="17" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="13"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCCE2C15-3BD9-4A19-9ABF-E289681724C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A58257D-F368-4BBA-B516-3E56F0E1148A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="124">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -401,6 +401,9 @@
   </si>
   <si>
     <t>started a new book</t>
+  </si>
+  <si>
+    <t>Went grocery shopping for the week</t>
   </si>
 </sst>
 </file>
@@ -4495,48 +4498,96 @@
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="13"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="15" t="str">
+      <c r="A77" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B77" s="14">
+        <v>240</v>
+      </c>
+      <c r="C77" s="14">
+        <v>0</v>
+      </c>
+      <c r="D77" s="14">
+        <v>120</v>
+      </c>
+      <c r="E77" s="14">
+        <v>20</v>
+      </c>
+      <c r="F77" s="14">
+        <v>200</v>
+      </c>
+      <c r="G77" s="14">
+        <v>4</v>
+      </c>
+      <c r="H77" s="14">
+        <v>240</v>
+      </c>
+      <c r="I77" s="15">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J77" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J77" s="15">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
-      <c r="N77" s="17"/>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="13"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="15" t="str">
+        <v>620</v>
+      </c>
+      <c r="K77" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L77" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M77" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N77" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A78" s="13">
+        <v>46325</v>
+      </c>
+      <c r="B78" s="14">
+        <v>420</v>
+      </c>
+      <c r="C78" s="14">
+        <v>60</v>
+      </c>
+      <c r="D78" s="14">
+        <v>240</v>
+      </c>
+      <c r="E78" s="14">
+        <v>0</v>
+      </c>
+      <c r="F78" s="14">
+        <v>200</v>
+      </c>
+      <c r="G78" s="14">
+        <v>4</v>
+      </c>
+      <c r="H78" s="14">
+        <v>180</v>
+      </c>
+      <c r="I78" s="15">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J78" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J78" s="15">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="16"/>
-      <c r="N78" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K78" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L78" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M78" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N78" s="17" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="13"/>
